--- a/SmartBooks.HumanResource/bin/x86/Debug/Teamleate/DanhSachNhanVienActive.xlsx
+++ b/SmartBooks.HumanResource/bin/x86/Debug/Teamleate/DanhSachNhanVienActive.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SourceCodeHR\SnK_Dev\SmartBooks.HumanResource\bin\x86\Debug\Teamleate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E646EED-33DA-4B46-B536-4DEDED3C7535}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{452D8215-C2B0-4047-9210-6CA3015342EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -94,7 +94,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="92">
   <si>
     <t>STT
 No.</t>
@@ -325,21 +325,9 @@
     <t>Address_Permanent</t>
   </si>
   <si>
-    <t>Tinh_TP_ThuongTru</t>
-  </si>
-  <si>
-    <t>Huyen_ThiXa_ThuongTru</t>
-  </si>
-  <si>
-    <t>Xa_Phuong_ThuongTru</t>
-  </si>
-  <si>
     <t>NativePlace</t>
   </si>
   <si>
-    <t>Factory_ID</t>
-  </si>
-  <si>
     <t>BankAccount</t>
   </si>
   <si>
@@ -370,9 +358,6 @@
     <t>TonGiao</t>
   </si>
   <si>
-    <t>SoNha_ThuongTru</t>
-  </si>
-  <si>
     <t>TernimationDate</t>
   </si>
   <si>
@@ -416,6 +401,9 @@
   </si>
   <si>
     <t>Nation</t>
+  </si>
+  <si>
+    <t>FactoryName</t>
   </si>
 </sst>
 </file>
@@ -582,13 +570,13 @@
     <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -917,331 +905,331 @@
       <c r="A2">
         <v>2</v>
       </c>
-      <c r="F2" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
+      <c r="F2" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
     </row>
     <row r="3" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="F3" s="10" t="str">
+      <c r="F3" s="11" t="str">
         <f ca="1">"Tháng "&amp;MONTH(IF(A1="NULL",TODAY(),A1))&amp;"-"&amp;YEAR(IF(A1="NULL",TODAY(),A1))</f>
         <v>Tháng 1-1900</v>
       </c>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
-      <c r="N3" s="10"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="11"/>
     </row>
-    <row r="4" spans="1:52" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="11">
-        <v>2</v>
-      </c>
-      <c r="C4" s="11">
-        <v>2</v>
-      </c>
-      <c r="D4" s="11">
-        <v>2</v>
-      </c>
-      <c r="E4" s="11">
-        <v>2</v>
-      </c>
-      <c r="F4" s="11">
-        <v>2</v>
-      </c>
-      <c r="G4" s="11">
-        <v>2</v>
-      </c>
-      <c r="H4" s="11">
-        <v>2</v>
-      </c>
-      <c r="I4" s="11">
-        <v>2</v>
-      </c>
-      <c r="J4" s="11">
-        <v>2</v>
-      </c>
-      <c r="K4" s="11">
-        <v>2</v>
-      </c>
-      <c r="L4" s="11">
-        <v>2</v>
-      </c>
-      <c r="M4" s="11">
-        <v>2</v>
-      </c>
-      <c r="N4" s="11">
-        <v>2</v>
-      </c>
-      <c r="O4" s="11">
-        <v>2</v>
-      </c>
-      <c r="P4" s="11">
-        <v>2</v>
-      </c>
-      <c r="Q4" s="11">
-        <v>2</v>
-      </c>
-      <c r="R4" s="11">
-        <v>2</v>
-      </c>
-      <c r="S4" s="11">
-        <v>2</v>
-      </c>
-      <c r="T4" s="11">
-        <v>2</v>
-      </c>
-      <c r="U4" s="11">
-        <v>2</v>
-      </c>
-      <c r="V4" s="11">
-        <v>2</v>
-      </c>
-      <c r="W4" s="11">
-        <v>2</v>
-      </c>
-      <c r="X4" s="11">
-        <v>2</v>
-      </c>
-      <c r="Y4" s="11">
-        <v>2</v>
-      </c>
-      <c r="Z4" s="11">
-        <v>2</v>
-      </c>
-      <c r="AA4" s="11">
-        <v>2</v>
-      </c>
-      <c r="AB4" s="11">
-        <v>2</v>
-      </c>
-      <c r="AC4" s="11">
-        <v>2</v>
-      </c>
-      <c r="AD4" s="11">
-        <v>2</v>
-      </c>
-      <c r="AE4" s="11">
-        <v>2</v>
-      </c>
-      <c r="AF4" s="11">
-        <v>2</v>
-      </c>
-      <c r="AG4" s="11">
-        <v>2</v>
-      </c>
-      <c r="AH4" s="11">
-        <v>2</v>
-      </c>
-      <c r="AI4" s="11">
-        <v>2</v>
-      </c>
-      <c r="AJ4" s="11">
-        <v>2</v>
-      </c>
-      <c r="AK4" s="11">
-        <v>2</v>
-      </c>
-      <c r="AL4" s="11">
-        <v>2</v>
-      </c>
-      <c r="AM4" s="11">
-        <v>2</v>
-      </c>
-      <c r="AN4" s="11">
-        <v>2</v>
-      </c>
-      <c r="AO4" s="11">
-        <v>2</v>
-      </c>
-      <c r="AP4" s="11">
-        <v>2</v>
-      </c>
-      <c r="AQ4" s="11">
-        <v>2</v>
-      </c>
-      <c r="AR4" s="11">
-        <v>2</v>
-      </c>
-      <c r="AS4" s="11">
-        <v>2</v>
-      </c>
-      <c r="AT4" s="11">
-        <v>2</v>
-      </c>
-      <c r="AU4" s="11">
-        <v>2</v>
-      </c>
-      <c r="AV4" s="11">
-        <v>2</v>
-      </c>
-      <c r="AW4" s="11">
-        <v>2</v>
-      </c>
-      <c r="AX4" s="11">
-        <v>2</v>
-      </c>
-      <c r="AY4" s="11">
-        <v>2</v>
-      </c>
-      <c r="AZ4" s="11">
+    <row r="4" spans="1:52" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="9">
+        <v>2</v>
+      </c>
+      <c r="C4" s="9">
+        <v>2</v>
+      </c>
+      <c r="D4" s="9">
+        <v>2</v>
+      </c>
+      <c r="E4" s="9">
+        <v>2</v>
+      </c>
+      <c r="F4" s="9">
+        <v>2</v>
+      </c>
+      <c r="G4" s="9">
+        <v>2</v>
+      </c>
+      <c r="H4" s="9">
+        <v>2</v>
+      </c>
+      <c r="I4" s="9">
+        <v>2</v>
+      </c>
+      <c r="J4" s="9">
+        <v>2</v>
+      </c>
+      <c r="K4" s="9">
+        <v>2</v>
+      </c>
+      <c r="L4" s="9">
+        <v>2</v>
+      </c>
+      <c r="M4" s="9">
+        <v>2</v>
+      </c>
+      <c r="N4" s="9">
+        <v>2</v>
+      </c>
+      <c r="O4" s="9">
+        <v>2</v>
+      </c>
+      <c r="P4" s="9">
+        <v>2</v>
+      </c>
+      <c r="Q4" s="9">
+        <v>2</v>
+      </c>
+      <c r="R4" s="9">
+        <v>2</v>
+      </c>
+      <c r="S4" s="9">
+        <v>2</v>
+      </c>
+      <c r="T4" s="9">
+        <v>2</v>
+      </c>
+      <c r="U4" s="9">
+        <v>2</v>
+      </c>
+      <c r="V4" s="9">
+        <v>2</v>
+      </c>
+      <c r="W4" s="9">
+        <v>2</v>
+      </c>
+      <c r="X4" s="9">
+        <v>2</v>
+      </c>
+      <c r="Y4" s="9">
+        <v>2</v>
+      </c>
+      <c r="Z4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AA4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AB4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AC4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AD4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AE4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AF4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AG4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AH4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AI4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AJ4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AK4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AL4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AM4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AN4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AO4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AP4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AQ4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AR4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AS4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AT4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AU4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AV4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AW4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AX4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AY4" s="9">
+        <v>2</v>
+      </c>
+      <c r="AZ4" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:52" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="11" t="s">
+    <row r="5" spans="1:52" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="M5" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="N5" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="O5" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="P5" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q5" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="R5" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="S5" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="T5" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="U5" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="V5" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="W5" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="X5" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y5" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z5" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA5" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB5" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC5" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD5" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="AE5" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AF5" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AG5" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="AH5" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI5" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="G5" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="K5" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="L5" s="11" t="s">
+      <c r="AJ5" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="M5" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="N5" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="O5" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="P5" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q5" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="R5" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="S5" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="T5" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="U5" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="V5" s="11" t="s">
+      <c r="AK5" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="AL5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM5" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="AN5" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="AO5" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="AP5" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="AQ5" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="AR5" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="AS5" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="AT5" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="AU5" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="W5" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="X5" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="Y5" s="11" t="s">
+      <c r="AV5" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="Z5" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA5" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="AB5" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="AC5" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="AD5" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE5" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="AF5" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="AG5" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="AH5" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI5" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="AJ5" s="11" t="s">
+      <c r="AW5" s="9" t="s">
         <v>81</v>
-      </c>
-      <c r="AK5" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="AL5" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM5" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="AN5" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="AO5" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="AP5" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="AQ5" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="AR5" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="AS5" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="AT5" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="AU5" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="AV5" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="AW5" s="11" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:52" ht="42" x14ac:dyDescent="0.25">

--- a/SmartBooks.HumanResource/bin/x86/Debug/Teamleate/DanhSachNhanVienActive.xlsx
+++ b/SmartBooks.HumanResource/bin/x86/Debug/Teamleate/DanhSachNhanVienActive.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SourceCodeHR\SnK_Dev\SmartBooks.HumanResource\bin\x86\Debug\Teamleate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{452D8215-C2B0-4047-9210-6CA3015342EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AE061C1-D7D8-4512-AF0A-2DF8EE9A215D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
